--- a/testing/FastFood_Testing_Plan.xlsx
+++ b/testing/FastFood_Testing_Plan.xlsx
@@ -1406,16 +1406,16 @@
         <v>PC-04</v>
       </c>
       <c r="B34" t="str">
-        <v>36.51</v>
+        <v>35.84</v>
       </c>
       <c r="C34" t="str">
-        <v>36.51</v>
+        <v>35.84</v>
       </c>
       <c r="D34" t="str">
         <v>PASS</v>
       </c>
       <c r="E34" t="str">
-        <v>Casual L1 evening (1.10× casual base). Pay guide says $35.84 — possible seed issue</v>
+        <v>Casual L1 evening (casual base + FT×10%)</v>
       </c>
     </row>
   </sheetData>
